--- a/XLibur.Tests/Resource/Examples/Misc/AdjustToContents.xlsx
+++ b/XLibur.Tests/Resource/Examples/Misc/AdjustToContents.xlsx
@@ -3391,14 +3391,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
-  <x:sheetPr>
-    <x:outlinePr summaryBelow="1" summaryRight="1"/>
-  </x:sheetPr>
   <x:dimension ref="A1:B8"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="31.996339" style="0" customWidth="1"/>
-    <x:col min="2" max="2" width="28.853482" style="0" customWidth="1"/>
+    <x:col min="1" max="1" width="31.996339" customWidth="1"/>
+    <x:col min="2" max="2" width="28.853482" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:2" ht="37.5" customHeight="1">
@@ -3412,27 +3409,27 @@
       </x:c>
     </x:row>
     <x:row r="4" spans="1:2">
-      <x:c r="B4" s="0" t="s">
+      <x:c r="B4" t="s">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:2">
-      <x:c r="B5" s="0" t="s">
+      <x:c r="B5" t="s">
         <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:2">
-      <x:c r="B6" s="0" t="s">
+      <x:c r="B6" t="s">
         <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:2">
-      <x:c r="B7" s="0" t="s">
+      <x:c r="B7" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:2">
-      <x:c r="B8" s="0" t="s">
+      <x:c r="B8" t="s">
         <x:v>2</x:v>
       </x:c>
     </x:row>
@@ -3440,48 +3437,41 @@
   <x:mergeCells count="1">
     <x:mergeCell ref="B6:D6"/>
   </x:mergeCells>
-  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
-  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
-  <x:headerFooter/>
-  <x:tableParts count="0"/>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
-  <x:sheetPr>
-    <x:outlinePr summaryBelow="1" summaryRight="1"/>
-  </x:sheetPr>
   <x:dimension ref="A1:S1"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="1.853482" style="0" customWidth="1"/>
-    <x:col min="2" max="2" width="15.996339" style="0" customWidth="1"/>
-    <x:col min="3" max="3" width="16.139196" style="0" customWidth="1"/>
-    <x:col min="4" max="4" width="17.567768" style="0" customWidth="1"/>
-    <x:col min="5" max="5" width="17.424911" style="0" customWidth="1"/>
-    <x:col min="6" max="6" width="16.996339" style="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16.710625" style="0" customWidth="1"/>
-    <x:col min="8" max="8" width="16.282054" style="0" customWidth="1"/>
-    <x:col min="9" max="9" width="15.853482" style="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15.139196" style="0" customWidth="1"/>
-    <x:col min="11" max="11" width="14.424911" style="0" customWidth="1"/>
-    <x:col min="12" max="12" width="13.567768" style="0" customWidth="1"/>
-    <x:col min="13" max="13" width="12.710625" style="0" customWidth="1"/>
-    <x:col min="14" max="14" width="11.424911" style="0" customWidth="1"/>
-    <x:col min="15" max="15" width="10.282054" style="0" customWidth="1"/>
-    <x:col min="16" max="16" width="9.139196" style="0" customWidth="1"/>
-    <x:col min="17" max="17" width="7.996339" style="0" customWidth="1"/>
-    <x:col min="18" max="18" width="6.424911" style="0" customWidth="1"/>
-    <x:col min="19" max="19" width="5.139196" style="0" customWidth="1"/>
+    <x:col min="1" max="1" width="1.853482" customWidth="1"/>
+    <x:col min="2" max="2" width="15.996339" customWidth="1"/>
+    <x:col min="3" max="3" width="16.139196" customWidth="1"/>
+    <x:col min="4" max="4" width="17.567768" customWidth="1"/>
+    <x:col min="5" max="5" width="17.424911" customWidth="1"/>
+    <x:col min="6" max="6" width="16.996339" customWidth="1"/>
+    <x:col min="7" max="7" width="16.710625" customWidth="1"/>
+    <x:col min="8" max="8" width="16.282054" customWidth="1"/>
+    <x:col min="9" max="9" width="15.853482" customWidth="1"/>
+    <x:col min="10" max="10" width="15.139196" customWidth="1"/>
+    <x:col min="11" max="11" width="14.424911" customWidth="1"/>
+    <x:col min="12" max="12" width="13.567768" customWidth="1"/>
+    <x:col min="13" max="13" width="12.710625" customWidth="1"/>
+    <x:col min="14" max="14" width="11.424911" customWidth="1"/>
+    <x:col min="15" max="15" width="10.282054" customWidth="1"/>
+    <x:col min="16" max="16" width="9.139196" customWidth="1"/>
+    <x:col min="17" max="17" width="7.996339" customWidth="1"/>
+    <x:col min="18" max="18" width="6.424911" customWidth="1"/>
+    <x:col min="19" max="19" width="5.139196" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:19">
       <x:c r="A1" s="3" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="B1" s="0" t="s">
+      <x:c r="B1" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="C1" s="4" t="s">
@@ -3537,48 +3527,41 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
-  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
-  <x:headerFooter/>
-  <x:tableParts count="0"/>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
-  <x:sheetPr>
-    <x:outlinePr summaryBelow="1" summaryRight="1"/>
-  </x:sheetPr>
   <x:dimension ref="A1:S1"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="1.853482" style="0" customWidth="1"/>
-    <x:col min="2" max="2" width="53.139196" style="0" customWidth="1"/>
-    <x:col min="3" max="3" width="88.282054" style="0" customWidth="1"/>
-    <x:col min="4" max="4" width="88.853482" style="0" customWidth="1"/>
-    <x:col min="5" max="5" width="87.567768" style="0" customWidth="1"/>
-    <x:col min="6" max="6" width="85.853482" style="0" customWidth="1"/>
-    <x:col min="7" max="7" width="83.567768" style="0" customWidth="1"/>
-    <x:col min="8" max="8" width="80.424911" style="0" customWidth="1"/>
-    <x:col min="9" max="9" width="76.567768" style="0" customWidth="1"/>
-    <x:col min="10" max="10" width="72.282054" style="0" customWidth="1"/>
-    <x:col min="11" max="11" width="67.424911" style="0" customWidth="1"/>
-    <x:col min="12" max="12" width="62.139196" style="0" customWidth="1"/>
-    <x:col min="13" max="13" width="56.424911" style="0" customWidth="1"/>
-    <x:col min="14" max="14" width="50.282054" style="0" customWidth="1"/>
-    <x:col min="15" max="15" width="43.853482" style="0" customWidth="1"/>
-    <x:col min="16" max="16" width="36.710625" style="0" customWidth="1"/>
-    <x:col min="17" max="17" width="29.710625" style="0" customWidth="1"/>
-    <x:col min="18" max="18" width="22.424911" style="0" customWidth="1"/>
-    <x:col min="19" max="19" width="14.710625" style="0" customWidth="1"/>
+    <x:col min="1" max="1" width="1.853482" customWidth="1"/>
+    <x:col min="2" max="2" width="53.139196" customWidth="1"/>
+    <x:col min="3" max="3" width="88.282054" customWidth="1"/>
+    <x:col min="4" max="4" width="88.853482" customWidth="1"/>
+    <x:col min="5" max="5" width="87.567768" customWidth="1"/>
+    <x:col min="6" max="6" width="85.853482" customWidth="1"/>
+    <x:col min="7" max="7" width="83.567768" customWidth="1"/>
+    <x:col min="8" max="8" width="80.424911" customWidth="1"/>
+    <x:col min="9" max="9" width="76.567768" customWidth="1"/>
+    <x:col min="10" max="10" width="72.282054" customWidth="1"/>
+    <x:col min="11" max="11" width="67.424911" customWidth="1"/>
+    <x:col min="12" max="12" width="62.139196" customWidth="1"/>
+    <x:col min="13" max="13" width="56.424911" customWidth="1"/>
+    <x:col min="14" max="14" width="50.282054" customWidth="1"/>
+    <x:col min="15" max="15" width="43.853482" customWidth="1"/>
+    <x:col min="16" max="16" width="36.710625" customWidth="1"/>
+    <x:col min="17" max="17" width="29.710625" customWidth="1"/>
+    <x:col min="18" max="18" width="22.424911" customWidth="1"/>
+    <x:col min="19" max="19" width="14.710625" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:19">
       <x:c r="A1" s="3" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="B1" s="0" t="s">
+      <x:c r="B1" t="s">
         <x:v>25</x:v>
       </x:c>
       <x:c r="C1" s="4" t="s">
@@ -3634,19 +3617,12 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
-  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
-  <x:headerFooter/>
-  <x:tableParts count="0"/>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
-  <x:sheetPr>
-    <x:outlinePr summaryBelow="1" summaryRight="1"/>
-  </x:sheetPr>
   <x:dimension ref="A1:A19"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
@@ -3656,7 +3632,7 @@
       </x:c>
     </x:row>
     <x:row r="2" spans="1:1" ht="14.25" customHeight="1">
-      <x:c r="A2" s="0" t="s">
+      <x:c r="A2" t="s">
         <x:v>7</x:v>
       </x:c>
     </x:row>
@@ -3746,19 +3722,12 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
-  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
-  <x:headerFooter/>
-  <x:tableParts count="0"/>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
-  <x:sheetPr>
-    <x:outlinePr summaryBelow="1" summaryRight="1"/>
-  </x:sheetPr>
   <x:dimension ref="A1:A19"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
@@ -3768,7 +3737,7 @@
       </x:c>
     </x:row>
     <x:row r="2" spans="1:1" ht="59.25" customHeight="1">
-      <x:c r="A2" s="0" t="s">
+      <x:c r="A2" t="s">
         <x:v>43</x:v>
       </x:c>
     </x:row>
@@ -3858,39 +3827,28 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
-  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
-  <x:headerFooter/>
-  <x:tableParts count="0"/>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
-  <x:sheetPr>
-    <x:outlinePr summaryBelow="1" summaryRight="1"/>
-  </x:sheetPr>
   <x:dimension ref="A1:B1"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="11.424911" style="0" customWidth="1"/>
-    <x:col min="2" max="2" width="255" style="0" customWidth="1"/>
+    <x:col min="1" max="1" width="11.424911" customWidth="1"/>
+    <x:col min="2" max="2" width="255" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:2">
-      <x:c r="A1" s="0" t="s">
+      <x:c r="A1" t="s">
         <x:v>61</x:v>
       </x:c>
-      <x:c r="B1" s="0" t="s">
+      <x:c r="B1" t="s">
         <x:v>62</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
-  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
-  <x:headerFooter/>
-  <x:tableParts count="0"/>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>
--- a/XLibur.Tests/Resource/Examples/Misc/AdjustToContents.xlsx
+++ b/XLibur.Tests/Resource/Examples/Misc/AdjustToContents.xlsx
@@ -3394,8 +3394,8 @@
   <x:dimension ref="A1:B8"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="31.996339" customWidth="1"/>
-    <x:col min="2" max="2" width="28.853482" customWidth="1"/>
+    <x:col min="1" max="1" width="31.282054" customWidth="1"/>
+    <x:col min="2" max="2" width="27.996339" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:2" ht="37.5" customHeight="1">
@@ -3446,23 +3446,23 @@
   <x:dimension ref="A1:S1"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="1.853482" customWidth="1"/>
-    <x:col min="2" max="2" width="15.996339" customWidth="1"/>
-    <x:col min="3" max="3" width="16.139196" customWidth="1"/>
-    <x:col min="4" max="4" width="17.567768" customWidth="1"/>
-    <x:col min="5" max="5" width="17.424911" customWidth="1"/>
-    <x:col min="6" max="6" width="16.996339" customWidth="1"/>
-    <x:col min="7" max="7" width="16.710625" customWidth="1"/>
-    <x:col min="8" max="8" width="16.282054" customWidth="1"/>
-    <x:col min="9" max="9" width="15.853482" customWidth="1"/>
-    <x:col min="10" max="10" width="15.139196" customWidth="1"/>
-    <x:col min="11" max="11" width="14.424911" customWidth="1"/>
-    <x:col min="12" max="12" width="13.567768" customWidth="1"/>
-    <x:col min="13" max="13" width="12.710625" customWidth="1"/>
-    <x:col min="14" max="14" width="11.424911" customWidth="1"/>
-    <x:col min="15" max="15" width="10.282054" customWidth="1"/>
-    <x:col min="16" max="16" width="9.139196" customWidth="1"/>
-    <x:col min="17" max="17" width="7.996339" customWidth="1"/>
+    <x:col min="1" max="1" width="2.139196" customWidth="1"/>
+    <x:col min="2" max="2" width="15.567768" customWidth="1"/>
+    <x:col min="3" max="3" width="15.710625" customWidth="1"/>
+    <x:col min="4" max="4" width="16.853482" customWidth="1"/>
+    <x:col min="5" max="5" width="16.710625" customWidth="1"/>
+    <x:col min="6" max="6" width="16.567768" customWidth="1"/>
+    <x:col min="7" max="7" width="16.282054" customWidth="1"/>
+    <x:col min="8" max="8" width="15.853482" customWidth="1"/>
+    <x:col min="9" max="9" width="15.424911" customWidth="1"/>
+    <x:col min="10" max="10" width="14.710625" customWidth="1"/>
+    <x:col min="11" max="11" width="13.996339" customWidth="1"/>
+    <x:col min="12" max="12" width="13.139196" customWidth="1"/>
+    <x:col min="13" max="13" width="12.139196" customWidth="1"/>
+    <x:col min="14" max="14" width="11.139196" customWidth="1"/>
+    <x:col min="15" max="15" width="9.996339" customWidth="1"/>
+    <x:col min="16" max="16" width="8.853482" customWidth="1"/>
+    <x:col min="17" max="17" width="7.710625" customWidth="1"/>
     <x:col min="18" max="18" width="6.424911" customWidth="1"/>
     <x:col min="19" max="19" width="5.139196" customWidth="1"/>
   </x:cols>
@@ -3536,25 +3536,25 @@
   <x:dimension ref="A1:S1"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="1.853482" customWidth="1"/>
-    <x:col min="2" max="2" width="53.139196" customWidth="1"/>
-    <x:col min="3" max="3" width="88.282054" customWidth="1"/>
-    <x:col min="4" max="4" width="88.853482" customWidth="1"/>
-    <x:col min="5" max="5" width="87.567768" customWidth="1"/>
-    <x:col min="6" max="6" width="85.853482" customWidth="1"/>
-    <x:col min="7" max="7" width="83.567768" customWidth="1"/>
-    <x:col min="8" max="8" width="80.424911" customWidth="1"/>
-    <x:col min="9" max="9" width="76.567768" customWidth="1"/>
-    <x:col min="10" max="10" width="72.282054" customWidth="1"/>
-    <x:col min="11" max="11" width="67.424911" customWidth="1"/>
-    <x:col min="12" max="12" width="62.139196" customWidth="1"/>
-    <x:col min="13" max="13" width="56.424911" customWidth="1"/>
-    <x:col min="14" max="14" width="50.282054" customWidth="1"/>
-    <x:col min="15" max="15" width="43.853482" customWidth="1"/>
-    <x:col min="16" max="16" width="36.710625" customWidth="1"/>
-    <x:col min="17" max="17" width="29.710625" customWidth="1"/>
-    <x:col min="18" max="18" width="22.424911" customWidth="1"/>
-    <x:col min="19" max="19" width="14.710625" customWidth="1"/>
+    <x:col min="1" max="1" width="2.139196" customWidth="1"/>
+    <x:col min="2" max="2" width="51.710625" customWidth="1"/>
+    <x:col min="3" max="3" width="85.996339" customWidth="1"/>
+    <x:col min="4" max="4" width="86.567768" customWidth="1"/>
+    <x:col min="5" max="5" width="85.567768" customWidth="1"/>
+    <x:col min="6" max="6" width="83.853482" customWidth="1"/>
+    <x:col min="7" max="7" width="81.424911" customWidth="1"/>
+    <x:col min="8" max="8" width="78.424911" customWidth="1"/>
+    <x:col min="9" max="9" width="74.710625" customWidth="1"/>
+    <x:col min="10" max="10" width="70.567768" customWidth="1"/>
+    <x:col min="11" max="11" width="65.853482" customWidth="1"/>
+    <x:col min="12" max="12" width="60.710625" customWidth="1"/>
+    <x:col min="13" max="13" width="55.139196" customWidth="1"/>
+    <x:col min="14" max="14" width="48.996339" customWidth="1"/>
+    <x:col min="15" max="15" width="42.710625" customWidth="1"/>
+    <x:col min="16" max="16" width="35.853482" customWidth="1"/>
+    <x:col min="17" max="17" width="28.853482" customWidth="1"/>
+    <x:col min="18" max="18" width="21.710625" customWidth="1"/>
+    <x:col min="19" max="19" width="14.282054" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:19">
@@ -3836,7 +3836,7 @@
   <x:dimension ref="A1:B1"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="11.424911" customWidth="1"/>
+    <x:col min="1" max="1" width="11.139196" customWidth="1"/>
     <x:col min="2" max="2" width="255" customWidth="1"/>
   </x:cols>
   <x:sheetData>

--- a/XLibur.Tests/Resource/Examples/Misc/AdjustToContents.xlsx
+++ b/XLibur.Tests/Resource/Examples/Misc/AdjustToContents.xlsx
@@ -3394,8 +3394,8 @@
   <x:dimension ref="A1:B8"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="31.282054" customWidth="1"/>
-    <x:col min="2" max="2" width="27.996339" customWidth="1"/>
+    <x:col min="1" max="1" width="31.285714" customWidth="1"/>
+    <x:col min="2" max="2" width="28" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:2" ht="37.5" customHeight="1">
@@ -3446,25 +3446,25 @@
   <x:dimension ref="A1:S1"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="2.139196" customWidth="1"/>
-    <x:col min="2" max="2" width="15.567768" customWidth="1"/>
-    <x:col min="3" max="3" width="15.710625" customWidth="1"/>
-    <x:col min="4" max="4" width="16.853482" customWidth="1"/>
-    <x:col min="5" max="5" width="16.710625" customWidth="1"/>
-    <x:col min="6" max="6" width="16.567768" customWidth="1"/>
-    <x:col min="7" max="7" width="16.282054" customWidth="1"/>
-    <x:col min="8" max="8" width="15.853482" customWidth="1"/>
-    <x:col min="9" max="9" width="15.424911" customWidth="1"/>
-    <x:col min="10" max="10" width="14.710625" customWidth="1"/>
-    <x:col min="11" max="11" width="13.996339" customWidth="1"/>
-    <x:col min="12" max="12" width="13.139196" customWidth="1"/>
-    <x:col min="13" max="13" width="12.139196" customWidth="1"/>
-    <x:col min="14" max="14" width="11.139196" customWidth="1"/>
-    <x:col min="15" max="15" width="9.996339" customWidth="1"/>
-    <x:col min="16" max="16" width="8.853482" customWidth="1"/>
-    <x:col min="17" max="17" width="7.710625" customWidth="1"/>
-    <x:col min="18" max="18" width="6.424911" customWidth="1"/>
-    <x:col min="19" max="19" width="5.139196" customWidth="1"/>
+    <x:col min="1" max="1" width="2.142857" customWidth="1"/>
+    <x:col min="2" max="2" width="15.571429" customWidth="1"/>
+    <x:col min="3" max="3" width="15.714286" customWidth="1"/>
+    <x:col min="4" max="4" width="16.857143" customWidth="1"/>
+    <x:col min="5" max="5" width="16.714286" customWidth="1"/>
+    <x:col min="6" max="6" width="16.571429" customWidth="1"/>
+    <x:col min="7" max="7" width="16.285714" customWidth="1"/>
+    <x:col min="8" max="8" width="15.857143" customWidth="1"/>
+    <x:col min="9" max="9" width="15.428571" customWidth="1"/>
+    <x:col min="10" max="10" width="14.714286" customWidth="1"/>
+    <x:col min="11" max="11" width="14" customWidth="1"/>
+    <x:col min="12" max="12" width="13.142857" customWidth="1"/>
+    <x:col min="13" max="13" width="12.142857" customWidth="1"/>
+    <x:col min="14" max="14" width="11.142857" customWidth="1"/>
+    <x:col min="15" max="15" width="10" customWidth="1"/>
+    <x:col min="16" max="16" width="8.857143" customWidth="1"/>
+    <x:col min="17" max="17" width="7.714286" customWidth="1"/>
+    <x:col min="18" max="18" width="6.428571" customWidth="1"/>
+    <x:col min="19" max="19" width="5.142857" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:19">
@@ -3536,25 +3536,25 @@
   <x:dimension ref="A1:S1"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="2.139196" customWidth="1"/>
-    <x:col min="2" max="2" width="51.710625" customWidth="1"/>
-    <x:col min="3" max="3" width="85.996339" customWidth="1"/>
-    <x:col min="4" max="4" width="86.567768" customWidth="1"/>
-    <x:col min="5" max="5" width="85.567768" customWidth="1"/>
-    <x:col min="6" max="6" width="83.853482" customWidth="1"/>
-    <x:col min="7" max="7" width="81.424911" customWidth="1"/>
-    <x:col min="8" max="8" width="78.424911" customWidth="1"/>
-    <x:col min="9" max="9" width="74.710625" customWidth="1"/>
-    <x:col min="10" max="10" width="70.567768" customWidth="1"/>
-    <x:col min="11" max="11" width="65.853482" customWidth="1"/>
-    <x:col min="12" max="12" width="60.710625" customWidth="1"/>
-    <x:col min="13" max="13" width="55.139196" customWidth="1"/>
-    <x:col min="14" max="14" width="48.996339" customWidth="1"/>
-    <x:col min="15" max="15" width="42.710625" customWidth="1"/>
-    <x:col min="16" max="16" width="35.853482" customWidth="1"/>
-    <x:col min="17" max="17" width="28.853482" customWidth="1"/>
-    <x:col min="18" max="18" width="21.710625" customWidth="1"/>
-    <x:col min="19" max="19" width="14.282054" customWidth="1"/>
+    <x:col min="1" max="1" width="2.142857" customWidth="1"/>
+    <x:col min="2" max="2" width="51.714286" customWidth="1"/>
+    <x:col min="3" max="3" width="86" customWidth="1"/>
+    <x:col min="4" max="4" width="86.571429" customWidth="1"/>
+    <x:col min="5" max="5" width="85.571429" customWidth="1"/>
+    <x:col min="6" max="6" width="83.857143" customWidth="1"/>
+    <x:col min="7" max="7" width="81.428571" customWidth="1"/>
+    <x:col min="8" max="8" width="78.428571" customWidth="1"/>
+    <x:col min="9" max="9" width="74.714286" customWidth="1"/>
+    <x:col min="10" max="10" width="70.571429" customWidth="1"/>
+    <x:col min="11" max="11" width="65.857143" customWidth="1"/>
+    <x:col min="12" max="12" width="60.714286" customWidth="1"/>
+    <x:col min="13" max="13" width="55.142857" customWidth="1"/>
+    <x:col min="14" max="14" width="49" customWidth="1"/>
+    <x:col min="15" max="15" width="42.714286" customWidth="1"/>
+    <x:col min="16" max="16" width="35.857143" customWidth="1"/>
+    <x:col min="17" max="17" width="28.857143" customWidth="1"/>
+    <x:col min="18" max="18" width="21.714286" customWidth="1"/>
+    <x:col min="19" max="19" width="14.285714" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:19">
@@ -3836,7 +3836,7 @@
   <x:dimension ref="A1:B1"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="11.139196" customWidth="1"/>
+    <x:col min="1" max="1" width="11.142857" customWidth="1"/>
     <x:col min="2" max="2" width="255" customWidth="1"/>
   </x:cols>
   <x:sheetData>
